--- a/public/downloads/sms-reminder-sample.xlsx
+++ b/public/downloads/sms-reminder-sample.xlsx
@@ -1,54 +1,68 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="SMS Reminder" sheetId="1" r:id="rId4"/>
+    <sheet name="SMS Reminder" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>PRODUCT_LABEL</t>
+    <t xml:space="preserve">PRODUCT_LABEL</t>
   </si>
   <si>
-    <t>SMS_1</t>
+    <t xml:space="preserve">SMS_1</t>
   </si>
   <si>
-    <t>SMS_2</t>
+    <t xml:space="preserve">SMS_2</t>
   </si>
   <si>
-    <t>DATASET_MONTH</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
+    <t xml:space="preserve">DATASET_MONTH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="4">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -60,7 +74,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -68,29 +82,57 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -125,302 +167,170 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="true" style="0"/>
-    <col min="2" max="2" width="22" customWidth="true" style="0"/>
-    <col min="3" max="3" width="22" customWidth="true" style="0"/>
-    <col min="4" max="4" width="22" customWidth="true" style="0"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>9123456789</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2">
-        <v>202610</v>
-      </c>
-    </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
   </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>